--- a/artfynd/A 53043-2023 artfynd.xlsx
+++ b/artfynd/A 53043-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53043-2023 artfynd.xlsx
+++ b/artfynd/A 53043-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111481831</v>
+        <v>111481839</v>
       </c>
       <c r="B2" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Allberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521851.5422416737</v>
+        <v>521852</v>
       </c>
       <c r="R2" t="n">
-        <v>7096229.993669239</v>
+        <v>7096230</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,19 +743,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111481839</v>
+        <v>111481834</v>
       </c>
       <c r="B3" t="n">
-        <v>76918</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521851.5422416737</v>
+        <v>521846</v>
       </c>
       <c r="R3" t="n">
-        <v>7096229.993669239</v>
+        <v>7096241</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,19 +840,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111481834</v>
+        <v>111481831</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Allberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521846.6308967983</v>
+        <v>521852</v>
       </c>
       <c r="R4" t="n">
-        <v>7096240.933028234</v>
+        <v>7096230</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,19 +945,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 53043-2023 artfynd.xlsx
+++ b/artfynd/A 53043-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481834</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,8 +986,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481831</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>